--- a/challenges_with_points.xlsx
+++ b/challenges_with_points.xlsx
@@ -37,169 +37,169 @@
     <t>Points</t>
   </si>
   <si>
-    <t>1762402177-9</t>
-  </si>
-  <si>
-    <t>1762402177-10</t>
-  </si>
-  <si>
-    <t>1762402177-11</t>
-  </si>
-  <si>
-    <t>1762402177-12</t>
-  </si>
-  <si>
-    <t>1762402177-13</t>
-  </si>
-  <si>
-    <t>1762402177-14</t>
-  </si>
-  <si>
-    <t>1762402177-15</t>
-  </si>
-  <si>
-    <t>1762402177-16</t>
-  </si>
-  <si>
-    <t>1762402177-17</t>
-  </si>
-  <si>
-    <t>1762402177-18</t>
-  </si>
-  <si>
-    <t>1762402177-19</t>
-  </si>
-  <si>
-    <t>1762402177-20</t>
-  </si>
-  <si>
-    <t>1762402177-21</t>
-  </si>
-  <si>
-    <t>1762402177-22</t>
-  </si>
-  <si>
-    <t>1762402177-23</t>
-  </si>
-  <si>
-    <t>1762402177-24</t>
-  </si>
-  <si>
-    <t>1762402177-25</t>
-  </si>
-  <si>
-    <t>1762402177-26</t>
-  </si>
-  <si>
-    <t>1762402177-27</t>
-  </si>
-  <si>
-    <t>1762402177-28</t>
-  </si>
-  <si>
-    <t>1762402177-29</t>
-  </si>
-  <si>
-    <t>1762402177-30</t>
-  </si>
-  <si>
-    <t>1762402177-31</t>
-  </si>
-  <si>
-    <t>1762402177-32</t>
-  </si>
-  <si>
-    <t>1762402177-33</t>
-  </si>
-  <si>
-    <t>1762402177-34</t>
-  </si>
-  <si>
-    <t>1762402177-35</t>
-  </si>
-  <si>
-    <t>1762402177-36</t>
-  </si>
-  <si>
-    <t>1762402177-37</t>
-  </si>
-  <si>
-    <t>1762402177-38</t>
-  </si>
-  <si>
-    <t>1762402177-39</t>
-  </si>
-  <si>
-    <t>1762402177-40</t>
-  </si>
-  <si>
-    <t>1762402177-41</t>
-  </si>
-  <si>
-    <t>1762402177-42</t>
-  </si>
-  <si>
-    <t>1762402177-43</t>
-  </si>
-  <si>
-    <t>1762402177-44</t>
-  </si>
-  <si>
-    <t>1762402177-45</t>
-  </si>
-  <si>
-    <t>1762402177-46</t>
-  </si>
-  <si>
-    <t>1762402177-47</t>
-  </si>
-  <si>
-    <t>1762402177-48</t>
-  </si>
-  <si>
-    <t>1762402177-49</t>
-  </si>
-  <si>
-    <t>1762402177-50</t>
-  </si>
-  <si>
-    <t>1762402177-51</t>
-  </si>
-  <si>
-    <t>1762402177-52</t>
-  </si>
-  <si>
-    <t>1762402177-53</t>
-  </si>
-  <si>
-    <t>1762402177-54</t>
-  </si>
-  <si>
-    <t>1762402177-55</t>
-  </si>
-  <si>
-    <t>1762402177-56</t>
-  </si>
-  <si>
-    <t>1762402177-57</t>
-  </si>
-  <si>
-    <t>1762402177-58</t>
-  </si>
-  <si>
-    <t>1762402177-59</t>
-  </si>
-  <si>
-    <t>1762402177-60</t>
-  </si>
-  <si>
-    <t>1762402177-61</t>
-  </si>
-  <si>
-    <t>1762402177-62</t>
-  </si>
-  <si>
-    <t>1762402177-63</t>
+    <t>1764947522-9</t>
+  </si>
+  <si>
+    <t>1764947522-10</t>
+  </si>
+  <si>
+    <t>1764947522-11</t>
+  </si>
+  <si>
+    <t>1764947522-12</t>
+  </si>
+  <si>
+    <t>1764947522-13</t>
+  </si>
+  <si>
+    <t>1764947522-14</t>
+  </si>
+  <si>
+    <t>1764947522-15</t>
+  </si>
+  <si>
+    <t>1764947522-16</t>
+  </si>
+  <si>
+    <t>1764947522-17</t>
+  </si>
+  <si>
+    <t>1764947522-18</t>
+  </si>
+  <si>
+    <t>1764947522-19</t>
+  </si>
+  <si>
+    <t>1764947522-20</t>
+  </si>
+  <si>
+    <t>1764947522-21</t>
+  </si>
+  <si>
+    <t>1764947522-22</t>
+  </si>
+  <si>
+    <t>1764947522-23</t>
+  </si>
+  <si>
+    <t>1764947522-24</t>
+  </si>
+  <si>
+    <t>1764947522-25</t>
+  </si>
+  <si>
+    <t>1764947522-26</t>
+  </si>
+  <si>
+    <t>1764947522-27</t>
+  </si>
+  <si>
+    <t>1764947522-28</t>
+  </si>
+  <si>
+    <t>1764947522-29</t>
+  </si>
+  <si>
+    <t>1764947522-30</t>
+  </si>
+  <si>
+    <t>1764947522-31</t>
+  </si>
+  <si>
+    <t>1764947522-32</t>
+  </si>
+  <si>
+    <t>1764947522-33</t>
+  </si>
+  <si>
+    <t>1764947522-34</t>
+  </si>
+  <si>
+    <t>1764947522-35</t>
+  </si>
+  <si>
+    <t>1764947522-36</t>
+  </si>
+  <si>
+    <t>1764947522-37</t>
+  </si>
+  <si>
+    <t>1764947522-38</t>
+  </si>
+  <si>
+    <t>1764947522-39</t>
+  </si>
+  <si>
+    <t>1764947522-40</t>
+  </si>
+  <si>
+    <t>1764947522-41</t>
+  </si>
+  <si>
+    <t>1764947522-42</t>
+  </si>
+  <si>
+    <t>1764947522-43</t>
+  </si>
+  <si>
+    <t>1764947522-44</t>
+  </si>
+  <si>
+    <t>1764947522-45</t>
+  </si>
+  <si>
+    <t>1764947522-46</t>
+  </si>
+  <si>
+    <t>1764947522-47</t>
+  </si>
+  <si>
+    <t>1764947522-48</t>
+  </si>
+  <si>
+    <t>1764947522-49</t>
+  </si>
+  <si>
+    <t>1764947522-50</t>
+  </si>
+  <si>
+    <t>1764947522-51</t>
+  </si>
+  <si>
+    <t>1764947522-52</t>
+  </si>
+  <si>
+    <t>1764947522-53</t>
+  </si>
+  <si>
+    <t>1764947522-54</t>
+  </si>
+  <si>
+    <t>1764947522-55</t>
+  </si>
+  <si>
+    <t>1764947522-56</t>
+  </si>
+  <si>
+    <t>1764947522-57</t>
+  </si>
+  <si>
+    <t>1764947522-58</t>
+  </si>
+  <si>
+    <t>1764947522-59</t>
+  </si>
+  <si>
+    <t>1764947522-60</t>
+  </si>
+  <si>
+    <t>1764947522-61</t>
+  </si>
+  <si>
+    <t>1764947522-62</t>
+  </si>
+  <si>
+    <t>1764947522-63</t>
   </si>
   <si>
     <t>https://conan.cote.ws/admin/db/challenge/</t>
@@ -781,10 +781,10 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -850,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G5">
-        <v>400</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -896,10 +896,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1057,10 +1057,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1149,10 +1149,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1195,10 +1195,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1356,7 +1356,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27">
         <v>50</v>
@@ -1379,7 +1379,7 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28">
         <v>50</v>
@@ -1425,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30">
-        <v>450</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1448,7 +1448,7 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G31">
         <v>50</v>
@@ -1540,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="F35">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G35">
         <v>50</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G36">
         <v>50</v>
@@ -1655,7 +1655,7 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G40">
         <v>50</v>
@@ -1724,7 +1724,7 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G43">
         <v>50</v>
@@ -1747,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G44">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1793,7 +1793,7 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G46">
         <v>50</v>
@@ -1839,10 +1839,10 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G48">
-        <v>150</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1977,7 +1977,7 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G54">
         <v>50</v>

--- a/challenges_with_points.xlsx
+++ b/challenges_with_points.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="116">
   <si>
     <t>web-scraper-order</t>
   </si>
@@ -37,169 +37,166 @@
     <t>Points</t>
   </si>
   <si>
-    <t>1764947522-9</t>
-  </si>
-  <si>
-    <t>1764947522-10</t>
-  </si>
-  <si>
-    <t>1764947522-11</t>
-  </si>
-  <si>
-    <t>1764947522-12</t>
-  </si>
-  <si>
-    <t>1764947522-13</t>
-  </si>
-  <si>
-    <t>1764947522-14</t>
-  </si>
-  <si>
-    <t>1764947522-15</t>
-  </si>
-  <si>
-    <t>1764947522-16</t>
-  </si>
-  <si>
-    <t>1764947522-17</t>
-  </si>
-  <si>
-    <t>1764947522-18</t>
-  </si>
-  <si>
-    <t>1764947522-19</t>
-  </si>
-  <si>
-    <t>1764947522-20</t>
-  </si>
-  <si>
-    <t>1764947522-21</t>
-  </si>
-  <si>
-    <t>1764947522-22</t>
-  </si>
-  <si>
-    <t>1764947522-23</t>
-  </si>
-  <si>
-    <t>1764947522-24</t>
-  </si>
-  <si>
-    <t>1764947522-25</t>
-  </si>
-  <si>
-    <t>1764947522-26</t>
-  </si>
-  <si>
-    <t>1764947522-27</t>
-  </si>
-  <si>
-    <t>1764947522-28</t>
-  </si>
-  <si>
-    <t>1764947522-29</t>
-  </si>
-  <si>
-    <t>1764947522-30</t>
-  </si>
-  <si>
-    <t>1764947522-31</t>
-  </si>
-  <si>
-    <t>1764947522-32</t>
-  </si>
-  <si>
-    <t>1764947522-33</t>
-  </si>
-  <si>
-    <t>1764947522-34</t>
-  </si>
-  <si>
-    <t>1764947522-35</t>
-  </si>
-  <si>
-    <t>1764947522-36</t>
-  </si>
-  <si>
-    <t>1764947522-37</t>
-  </si>
-  <si>
-    <t>1764947522-38</t>
-  </si>
-  <si>
-    <t>1764947522-39</t>
-  </si>
-  <si>
-    <t>1764947522-40</t>
-  </si>
-  <si>
-    <t>1764947522-41</t>
-  </si>
-  <si>
-    <t>1764947522-42</t>
-  </si>
-  <si>
-    <t>1764947522-43</t>
-  </si>
-  <si>
-    <t>1764947522-44</t>
-  </si>
-  <si>
-    <t>1764947522-45</t>
-  </si>
-  <si>
-    <t>1764947522-46</t>
-  </si>
-  <si>
-    <t>1764947522-47</t>
-  </si>
-  <si>
-    <t>1764947522-48</t>
-  </si>
-  <si>
-    <t>1764947522-49</t>
-  </si>
-  <si>
-    <t>1764947522-50</t>
-  </si>
-  <si>
-    <t>1764947522-51</t>
-  </si>
-  <si>
-    <t>1764947522-52</t>
-  </si>
-  <si>
-    <t>1764947522-53</t>
-  </si>
-  <si>
-    <t>1764947522-54</t>
-  </si>
-  <si>
-    <t>1764947522-55</t>
-  </si>
-  <si>
-    <t>1764947522-56</t>
-  </si>
-  <si>
-    <t>1764947522-57</t>
-  </si>
-  <si>
-    <t>1764947522-58</t>
-  </si>
-  <si>
-    <t>1764947522-59</t>
-  </si>
-  <si>
-    <t>1764947522-60</t>
-  </si>
-  <si>
-    <t>1764947522-61</t>
-  </si>
-  <si>
-    <t>1764947522-62</t>
-  </si>
-  <si>
-    <t>1764947522-63</t>
+    <t>1764948175-9</t>
+  </si>
+  <si>
+    <t>1764948175-10</t>
+  </si>
+  <si>
+    <t>1764948175-11</t>
+  </si>
+  <si>
+    <t>1764948175-12</t>
+  </si>
+  <si>
+    <t>1764948175-13</t>
+  </si>
+  <si>
+    <t>1764948175-14</t>
+  </si>
+  <si>
+    <t>1764948175-15</t>
+  </si>
+  <si>
+    <t>1764948175-16</t>
+  </si>
+  <si>
+    <t>1764948175-17</t>
+  </si>
+  <si>
+    <t>1764948175-18</t>
+  </si>
+  <si>
+    <t>1764948175-19</t>
+  </si>
+  <si>
+    <t>1764948175-20</t>
+  </si>
+  <si>
+    <t>1764948175-21</t>
+  </si>
+  <si>
+    <t>1764948175-22</t>
+  </si>
+  <si>
+    <t>1764948175-23</t>
+  </si>
+  <si>
+    <t>1764948175-24</t>
+  </si>
+  <si>
+    <t>1764948175-25</t>
+  </si>
+  <si>
+    <t>1764948175-26</t>
+  </si>
+  <si>
+    <t>1764948175-27</t>
+  </si>
+  <si>
+    <t>1764948175-28</t>
+  </si>
+  <si>
+    <t>1764948175-29</t>
+  </si>
+  <si>
+    <t>1764948175-30</t>
+  </si>
+  <si>
+    <t>1764948175-31</t>
+  </si>
+  <si>
+    <t>1764948175-32</t>
+  </si>
+  <si>
+    <t>1764948175-33</t>
+  </si>
+  <si>
+    <t>1764948175-34</t>
+  </si>
+  <si>
+    <t>1764948175-35</t>
+  </si>
+  <si>
+    <t>1764948175-36</t>
+  </si>
+  <si>
+    <t>1764948175-37</t>
+  </si>
+  <si>
+    <t>1764948175-38</t>
+  </si>
+  <si>
+    <t>1764948175-39</t>
+  </si>
+  <si>
+    <t>1764948175-40</t>
+  </si>
+  <si>
+    <t>1764948175-41</t>
+  </si>
+  <si>
+    <t>1764948175-42</t>
+  </si>
+  <si>
+    <t>1764948175-43</t>
+  </si>
+  <si>
+    <t>1764948175-44</t>
+  </si>
+  <si>
+    <t>1764948175-45</t>
+  </si>
+  <si>
+    <t>1764948175-46</t>
+  </si>
+  <si>
+    <t>1764948175-47</t>
+  </si>
+  <si>
+    <t>1764948175-48</t>
+  </si>
+  <si>
+    <t>1764948175-49</t>
+  </si>
+  <si>
+    <t>1764948175-50</t>
+  </si>
+  <si>
+    <t>1764948175-51</t>
+  </si>
+  <si>
+    <t>1764948175-52</t>
+  </si>
+  <si>
+    <t>1764948175-53</t>
+  </si>
+  <si>
+    <t>1764948175-54</t>
+  </si>
+  <si>
+    <t>1764948175-55</t>
+  </si>
+  <si>
+    <t>1764948175-56</t>
+  </si>
+  <si>
+    <t>1764948175-57</t>
+  </si>
+  <si>
+    <t>1764948175-58</t>
+  </si>
+  <si>
+    <t>1764948175-59</t>
+  </si>
+  <si>
+    <t>1764948175-60</t>
+  </si>
+  <si>
+    <t>1764948175-61</t>
+  </si>
+  <si>
+    <t>1764948175-62</t>
   </si>
   <si>
     <t>https://conan.cote.ws/admin/db/challenge/</t>
@@ -209,9 +206,6 @@
   </si>
   <si>
     <t>Sector 3 by 9</t>
-  </si>
-  <si>
-    <t>Toxic Base64</t>
   </si>
   <si>
     <t>Emoji</t>
@@ -738,7 +732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -769,10 +763,10 @@
         <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
         <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>63</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
@@ -792,10 +786,10 @@
         <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D3" t="b">
         <v>0</v>
@@ -815,10 +809,10 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D4" t="b">
         <v>0</v>
@@ -827,10 +821,10 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G4">
-        <v>500</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -838,10 +832,10 @@
         <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D5" t="b">
         <v>0</v>
@@ -850,10 +844,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -861,10 +855,10 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
@@ -873,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -884,10 +878,10 @@
         <v>12</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
@@ -896,10 +890,10 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -907,10 +901,10 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -919,10 +913,10 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G8">
-        <v>500</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -930,10 +924,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -942,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -953,10 +947,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -965,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -976,10 +970,10 @@
         <v>16</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
@@ -988,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11">
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -999,10 +993,10 @@
         <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -1011,10 +1005,10 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1022,10 +1016,10 @@
         <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
@@ -1034,10 +1028,10 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G13">
-        <v>300</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1045,10 +1039,10 @@
         <v>19</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
@@ -1057,10 +1051,10 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G14">
-        <v>100</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1068,10 +1062,10 @@
         <v>20</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -1091,10 +1085,10 @@
         <v>21</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -1103,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1114,10 +1108,10 @@
         <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
@@ -1126,10 +1120,10 @@
         <v>0</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>50</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1137,10 +1131,10 @@
         <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
@@ -1149,10 +1143,10 @@
         <v>0</v>
       </c>
       <c r="F18">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G18">
-        <v>300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1160,10 +1154,10 @@
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -1172,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="F19">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>50</v>
@@ -1183,10 +1177,10 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
@@ -1195,10 +1189,10 @@
         <v>0</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G20">
-        <v>50</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1206,10 +1200,10 @@
         <v>26</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
@@ -1218,10 +1212,10 @@
         <v>0</v>
       </c>
       <c r="F21">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G21">
-        <v>150</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1229,10 +1223,10 @@
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -1241,10 +1235,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1252,10 +1246,10 @@
         <v>28</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -1264,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1275,10 +1269,10 @@
         <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -1287,10 +1281,10 @@
         <v>0</v>
       </c>
       <c r="F24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24">
-        <v>250</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1298,10 +1292,10 @@
         <v>30</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D25" t="b">
         <v>0</v>
@@ -1310,10 +1304,10 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G25">
-        <v>300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1321,10 +1315,10 @@
         <v>31</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
@@ -1333,7 +1327,7 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G26">
         <v>50</v>
@@ -1344,10 +1338,10 @@
         <v>32</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
@@ -1356,7 +1350,7 @@
         <v>0</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G27">
         <v>50</v>
@@ -1367,10 +1361,10 @@
         <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -1379,10 +1373,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G28">
-        <v>50</v>
+        <v>300</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1390,10 +1384,10 @@
         <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D29" t="b">
         <v>0</v>
@@ -1402,10 +1396,10 @@
         <v>0</v>
       </c>
       <c r="F29">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G29">
-        <v>300</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1413,10 +1407,10 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D30" t="b">
         <v>0</v>
@@ -1425,10 +1419,10 @@
         <v>0</v>
       </c>
       <c r="F30">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G30">
-        <v>400</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1436,10 +1430,10 @@
         <v>36</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
@@ -1448,10 +1442,10 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G31">
-        <v>50</v>
+        <v>350</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1459,10 +1453,10 @@
         <v>37</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D32" t="b">
         <v>0</v>
@@ -1471,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="F32">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G32">
-        <v>350</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1482,10 +1476,10 @@
         <v>38</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D33" t="b">
         <v>0</v>
@@ -1494,10 +1488,10 @@
         <v>0</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G33">
-        <v>250</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1505,10 +1499,10 @@
         <v>39</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D34" t="b">
         <v>0</v>
@@ -1517,10 +1511,10 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G34">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1528,10 +1522,10 @@
         <v>40</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D35" t="b">
         <v>0</v>
@@ -1551,10 +1545,10 @@
         <v>41</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D36" t="b">
         <v>0</v>
@@ -1574,10 +1568,10 @@
         <v>42</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D37" t="b">
         <v>0</v>
@@ -1586,10 +1580,10 @@
         <v>0</v>
       </c>
       <c r="F37">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G37">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1597,10 +1591,10 @@
         <v>43</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D38" t="b">
         <v>0</v>
@@ -1609,10 +1603,10 @@
         <v>0</v>
       </c>
       <c r="F38">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G38">
-        <v>100</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1620,10 +1614,10 @@
         <v>44</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D39" t="b">
         <v>0</v>
@@ -1632,10 +1626,10 @@
         <v>0</v>
       </c>
       <c r="F39">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="G39">
-        <v>300</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1643,10 +1637,10 @@
         <v>45</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D40" t="b">
         <v>0</v>
@@ -1655,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G40">
-        <v>50</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1666,10 +1660,10 @@
         <v>46</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D41" t="b">
         <v>0</v>
@@ -1678,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G41">
-        <v>300</v>
+        <v>350</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1689,10 +1683,10 @@
         <v>47</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D42" t="b">
         <v>0</v>
@@ -1701,10 +1695,10 @@
         <v>0</v>
       </c>
       <c r="F42">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G42">
-        <v>350</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1712,10 +1706,10 @@
         <v>48</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D43" t="b">
         <v>0</v>
@@ -1724,10 +1718,10 @@
         <v>0</v>
       </c>
       <c r="F43">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G43">
-        <v>50</v>
+        <v>250</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1735,10 +1729,10 @@
         <v>49</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D44" t="b">
         <v>0</v>
@@ -1747,10 +1741,10 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G44">
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1758,10 +1752,10 @@
         <v>50</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D45" t="b">
         <v>0</v>
@@ -1770,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G45">
         <v>50</v>
@@ -1781,10 +1775,10 @@
         <v>51</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D46" t="b">
         <v>0</v>
@@ -1793,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="F46">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G46">
-        <v>50</v>
+        <v>400</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1804,10 +1798,10 @@
         <v>52</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D47" t="b">
         <v>0</v>
@@ -1816,10 +1810,10 @@
         <v>0</v>
       </c>
       <c r="F47">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G47">
-        <v>400</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1827,10 +1821,10 @@
         <v>53</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D48" t="b">
         <v>0</v>
@@ -1839,10 +1833,10 @@
         <v>0</v>
       </c>
       <c r="F48">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G48">
-        <v>100</v>
+        <v>350</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1850,10 +1844,10 @@
         <v>54</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D49" t="b">
         <v>0</v>
@@ -1862,10 +1856,10 @@
         <v>0</v>
       </c>
       <c r="F49">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G49">
-        <v>350</v>
+        <v>150</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1873,10 +1867,10 @@
         <v>55</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D50" t="b">
         <v>0</v>
@@ -1885,10 +1879,10 @@
         <v>0</v>
       </c>
       <c r="F50">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="G50">
-        <v>150</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1896,10 +1890,10 @@
         <v>56</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D51" t="b">
         <v>0</v>
@@ -1908,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G51">
-        <v>50</v>
+        <v>400</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1919,10 +1913,10 @@
         <v>57</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D52" t="b">
         <v>0</v>
@@ -1931,10 +1925,10 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G52">
-        <v>400</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1942,10 +1936,10 @@
         <v>58</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D53" t="b">
         <v>0</v>
@@ -1954,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="G53">
-        <v>250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1965,10 +1959,10 @@
         <v>59</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D54" t="b">
         <v>0</v>
@@ -1977,10 +1971,10 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="G54">
-        <v>50</v>
+        <v>350</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1988,10 +1982,10 @@
         <v>60</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D55" t="b">
         <v>0</v>
@@ -2000,32 +1994,9 @@
         <v>0</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="G55">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" t="s">
-        <v>117</v>
-      </c>
-      <c r="D56" t="b">
-        <v>0</v>
-      </c>
-      <c r="E56" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56">
-        <v>34</v>
-      </c>
-      <c r="G56">
         <v>50</v>
       </c>
     </row>
@@ -2085,7 +2056,6 @@
     <hyperlink ref="B53" r:id="rId52"/>
     <hyperlink ref="B54" r:id="rId53"/>
     <hyperlink ref="B55" r:id="rId54"/>
-    <hyperlink ref="B56" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/challenges_with_points.xlsx
+++ b/challenges_with_points.xlsx
@@ -37,166 +37,166 @@
     <t>Points</t>
   </si>
   <si>
-    <t>1764948175-9</t>
-  </si>
-  <si>
-    <t>1764948175-10</t>
-  </si>
-  <si>
-    <t>1764948175-11</t>
-  </si>
-  <si>
-    <t>1764948175-12</t>
-  </si>
-  <si>
-    <t>1764948175-13</t>
-  </si>
-  <si>
-    <t>1764948175-14</t>
-  </si>
-  <si>
-    <t>1764948175-15</t>
-  </si>
-  <si>
-    <t>1764948175-16</t>
-  </si>
-  <si>
-    <t>1764948175-17</t>
-  </si>
-  <si>
-    <t>1764948175-18</t>
-  </si>
-  <si>
-    <t>1764948175-19</t>
-  </si>
-  <si>
-    <t>1764948175-20</t>
-  </si>
-  <si>
-    <t>1764948175-21</t>
-  </si>
-  <si>
-    <t>1764948175-22</t>
-  </si>
-  <si>
-    <t>1764948175-23</t>
-  </si>
-  <si>
-    <t>1764948175-24</t>
-  </si>
-  <si>
-    <t>1764948175-25</t>
-  </si>
-  <si>
-    <t>1764948175-26</t>
-  </si>
-  <si>
-    <t>1764948175-27</t>
-  </si>
-  <si>
-    <t>1764948175-28</t>
-  </si>
-  <si>
-    <t>1764948175-29</t>
-  </si>
-  <si>
-    <t>1764948175-30</t>
-  </si>
-  <si>
-    <t>1764948175-31</t>
-  </si>
-  <si>
-    <t>1764948175-32</t>
-  </si>
-  <si>
-    <t>1764948175-33</t>
-  </si>
-  <si>
-    <t>1764948175-34</t>
-  </si>
-  <si>
-    <t>1764948175-35</t>
-  </si>
-  <si>
-    <t>1764948175-36</t>
-  </si>
-  <si>
-    <t>1764948175-37</t>
-  </si>
-  <si>
-    <t>1764948175-38</t>
-  </si>
-  <si>
-    <t>1764948175-39</t>
-  </si>
-  <si>
-    <t>1764948175-40</t>
-  </si>
-  <si>
-    <t>1764948175-41</t>
-  </si>
-  <si>
-    <t>1764948175-42</t>
-  </si>
-  <si>
-    <t>1764948175-43</t>
-  </si>
-  <si>
-    <t>1764948175-44</t>
-  </si>
-  <si>
-    <t>1764948175-45</t>
-  </si>
-  <si>
-    <t>1764948175-46</t>
-  </si>
-  <si>
-    <t>1764948175-47</t>
-  </si>
-  <si>
-    <t>1764948175-48</t>
-  </si>
-  <si>
-    <t>1764948175-49</t>
-  </si>
-  <si>
-    <t>1764948175-50</t>
-  </si>
-  <si>
-    <t>1764948175-51</t>
-  </si>
-  <si>
-    <t>1764948175-52</t>
-  </si>
-  <si>
-    <t>1764948175-53</t>
-  </si>
-  <si>
-    <t>1764948175-54</t>
-  </si>
-  <si>
-    <t>1764948175-55</t>
-  </si>
-  <si>
-    <t>1764948175-56</t>
-  </si>
-  <si>
-    <t>1764948175-57</t>
-  </si>
-  <si>
-    <t>1764948175-58</t>
-  </si>
-  <si>
-    <t>1764948175-59</t>
-  </si>
-  <si>
-    <t>1764948175-60</t>
-  </si>
-  <si>
-    <t>1764948175-61</t>
-  </si>
-  <si>
-    <t>1764948175-62</t>
+    <t>1767629000-9</t>
+  </si>
+  <si>
+    <t>1767629000-10</t>
+  </si>
+  <si>
+    <t>1767629000-11</t>
+  </si>
+  <si>
+    <t>1767629000-12</t>
+  </si>
+  <si>
+    <t>1767629000-13</t>
+  </si>
+  <si>
+    <t>1767629000-14</t>
+  </si>
+  <si>
+    <t>1767629000-15</t>
+  </si>
+  <si>
+    <t>1767629000-16</t>
+  </si>
+  <si>
+    <t>1767629000-17</t>
+  </si>
+  <si>
+    <t>1767629000-18</t>
+  </si>
+  <si>
+    <t>1767629000-19</t>
+  </si>
+  <si>
+    <t>1767629000-20</t>
+  </si>
+  <si>
+    <t>1767629000-21</t>
+  </si>
+  <si>
+    <t>1767629000-22</t>
+  </si>
+  <si>
+    <t>1767629000-23</t>
+  </si>
+  <si>
+    <t>1767629000-24</t>
+  </si>
+  <si>
+    <t>1767629000-25</t>
+  </si>
+  <si>
+    <t>1767629000-26</t>
+  </si>
+  <si>
+    <t>1767629000-27</t>
+  </si>
+  <si>
+    <t>1767629000-28</t>
+  </si>
+  <si>
+    <t>1767629000-29</t>
+  </si>
+  <si>
+    <t>1767629000-30</t>
+  </si>
+  <si>
+    <t>1767629000-31</t>
+  </si>
+  <si>
+    <t>1767629000-32</t>
+  </si>
+  <si>
+    <t>1767629000-33</t>
+  </si>
+  <si>
+    <t>1767629000-34</t>
+  </si>
+  <si>
+    <t>1767629000-35</t>
+  </si>
+  <si>
+    <t>1767629000-36</t>
+  </si>
+  <si>
+    <t>1767629000-37</t>
+  </si>
+  <si>
+    <t>1767629000-38</t>
+  </si>
+  <si>
+    <t>1767629000-39</t>
+  </si>
+  <si>
+    <t>1767629000-40</t>
+  </si>
+  <si>
+    <t>1767629000-41</t>
+  </si>
+  <si>
+    <t>1767629000-42</t>
+  </si>
+  <si>
+    <t>1767629000-43</t>
+  </si>
+  <si>
+    <t>1767629000-44</t>
+  </si>
+  <si>
+    <t>1767629000-45</t>
+  </si>
+  <si>
+    <t>1767629000-46</t>
+  </si>
+  <si>
+    <t>1767629000-47</t>
+  </si>
+  <si>
+    <t>1767629000-48</t>
+  </si>
+  <si>
+    <t>1767629000-49</t>
+  </si>
+  <si>
+    <t>1767629000-50</t>
+  </si>
+  <si>
+    <t>1767629000-51</t>
+  </si>
+  <si>
+    <t>1767629000-52</t>
+  </si>
+  <si>
+    <t>1767629000-53</t>
+  </si>
+  <si>
+    <t>1767629000-54</t>
+  </si>
+  <si>
+    <t>1767629000-55</t>
+  </si>
+  <si>
+    <t>1767629000-56</t>
+  </si>
+  <si>
+    <t>1767629000-57</t>
+  </si>
+  <si>
+    <t>1767629000-58</t>
+  </si>
+  <si>
+    <t>1767629000-59</t>
+  </si>
+  <si>
+    <t>1767629000-60</t>
+  </si>
+  <si>
+    <t>1767629000-61</t>
+  </si>
+  <si>
+    <t>1767629000-62</t>
   </si>
   <si>
     <t>https://conan.cote.ws/admin/db/challenge/</t>
@@ -1235,10 +1235,10 @@
         <v>0</v>
       </c>
       <c r="F22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G22">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1258,10 +1258,10 @@
         <v>0</v>
       </c>
       <c r="F23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G23">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1304,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="F25">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G25">
         <v>50</v>
@@ -1373,10 +1373,10 @@
         <v>0</v>
       </c>
       <c r="F28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28">
-        <v>300</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1442,10 +1442,10 @@
         <v>0</v>
       </c>
       <c r="F31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G31">
-        <v>350</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1741,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="F44">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G44">
         <v>50</v>
@@ -1925,10 +1925,10 @@
         <v>0</v>
       </c>
       <c r="F52">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G52">
-        <v>250</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" spans="1:7">
